--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
   <si>
     <t>SOS</t>
   </si>
@@ -656,166 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43190</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E8" s="3">
         <v>41800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>127400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>84800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>106300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>184500</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>9900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E9" s="3">
         <v>41700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>150300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>82200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>110600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>167200</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>9800</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -837,35 +844,38 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-22900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-4300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17300</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -887,8 +897,11 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,8 +920,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -933,32 +947,35 @@
       <c r="J12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1007,17 +1024,20 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
@@ -1028,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>5700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
+      <c r="K14" s="3">
+        <v>5700</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
@@ -1042,23 +1062,26 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>-4400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>9100</v>
       </c>
       <c r="R14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="S14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1107,8 +1130,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,108 +1150,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E17" s="3">
         <v>54300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>326600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>106400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>129200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>204600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>41200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>29400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>80500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>46800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-199200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-22900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-20100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-30100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,85 +1277,89 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-18300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
         <v>21100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-212300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-32900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-14300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1344,8 +1381,11 @@
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1394,108 +1434,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-217500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-40400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-29800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1593,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-215300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-214900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1752,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1703,26 +1764,26 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>6900</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>3400</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3">
         <v>12000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-500</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1738,14 +1799,17 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1858,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,108 +1911,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>18300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
         <v>-21100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-215100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2070,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-215100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43190</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2204,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,58 +2225,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>279200</v>
+      </c>
+      <c r="E41" s="3">
         <v>249900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>259500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>247300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>338000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>185500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>39200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>58800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>71700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>94900</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2239,79 +2329,85 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E43" s="3">
         <v>117100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>129000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>335300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>214900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>60600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>32700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>34800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E44" s="3">
         <v>42500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>46300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>84900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>96100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>102600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2327,8 +2423,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2339,16 +2435,19 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
@@ -2356,18 +2455,18 @@
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>164300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>16800</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2383,14 +2482,17 @@
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2439,13 +2541,16 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>300</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
@@ -2465,82 +2570,88 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>600</v>
       </c>
       <c r="R47" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E48" s="3">
         <v>13100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2562,8 +2673,8 @@
       <c r="I49" s="3">
         <v>100</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+      <c r="J49" s="3">
+        <v>100</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -2580,8 +2691,8 @@
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2589,8 +2700,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2753,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,58 +2806,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>53700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>37100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>57600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,58 +2912,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>483900</v>
+      </c>
+      <c r="E54" s="3">
         <v>429300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>454700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>713000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>695300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>559700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>72700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>111500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>91100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>103800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>115000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +2988,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,37 +3009,38 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E57" s="3">
         <v>13900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>34900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29500</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2918,19 +3049,22 @@
         <v>0</v>
       </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>11100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2979,58 +3113,64 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E59" s="3">
         <v>25500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>33100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>64100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>91200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>131200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>93500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>60700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>56400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>51500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3079,8 +3219,11 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3129,8 +3272,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3146,18 +3292,18 @@
       <c r="G62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>50200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3173,14 +3319,17 @@
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3378,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3431,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,58 +3484,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E66" s="3">
         <v>37100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>75900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61900</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>9500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>70800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>64100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>92200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>132200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>95200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>76400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>78700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>79700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3560,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3611,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3664,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3717,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,58 +3770,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-276500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-283600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-272900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-43400</v>
       </c>
       <c r="G72" s="3">
         <v>-43400</v>
       </c>
       <c r="H72" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="I72" s="3">
         <v>-14600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-293100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-306000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-303800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-283200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-268300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-257300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-246700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-221700</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +3876,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +3929,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,58 +3982,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E76" s="3">
         <v>392300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>409600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>637100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>633400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>559800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-20300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-20700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>35300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4088,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43190</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-215100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,34 +4222,35 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5500</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
@@ -4068,14 +4267,17 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4326,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4379,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4432,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4485,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,58 +4538,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-104300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>120600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-339200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-43600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
         <v>-36600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-26900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,8 +4614,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4423,29 +4644,32 @@
       <c r="K91" s="3">
         <v>-10700</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
+      <c r="L91" s="3">
+        <v>-10700</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4718,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,8 +4771,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4553,49 +4783,52 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-17600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,8 +4847,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4664,8 +4898,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +4951,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5004,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,82 +5057,88 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>18500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>32300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>551800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>43600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>7700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4899,69 +5148,75 @@
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
         <v>-1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-90700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>149500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>184800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
         <v>-40700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-23200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>SOS</t>
   </si>
@@ -2449,8 +2449,8 @@
       <c r="E45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
+      <c r="F45" s="3">
+        <v>0</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>SOS</t>
   </si>
@@ -656,179 +656,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43373</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>50600</v>
+        <v>30300</v>
       </c>
       <c r="E8" s="3">
-        <v>41800</v>
+        <v>30300</v>
       </c>
       <c r="F8" s="3">
-        <v>127400</v>
+        <v>25300</v>
       </c>
       <c r="G8" s="3">
-        <v>84800</v>
+        <v>25300</v>
       </c>
       <c r="H8" s="3">
-        <v>106300</v>
+        <v>20900</v>
       </c>
       <c r="I8" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>87600</v>
+      </c>
+      <c r="K8" s="3">
         <v>184500</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>9900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>14200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>20800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>18100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>17600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>39800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>16700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>36500</v>
+        <v>29000</v>
       </c>
       <c r="E9" s="3">
-        <v>41700</v>
+        <v>29000</v>
       </c>
       <c r="F9" s="3">
-        <v>150300</v>
+        <v>18300</v>
       </c>
       <c r="G9" s="3">
-        <v>82200</v>
+        <v>18300</v>
       </c>
       <c r="H9" s="3">
-        <v>110600</v>
+        <v>20900</v>
       </c>
       <c r="I9" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>94200</v>
+      </c>
+      <c r="K9" s="3">
         <v>167200</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>9800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
@@ -847,41 +860,47 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>14100</v>
+        <v>1200</v>
       </c>
       <c r="E10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="K10" s="3">
+        <v>17300</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>-22900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>17300</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
-        <v>100</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -900,8 +919,14 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -921,8 +946,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -950,32 +977,38 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>4600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>8400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>4200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1027,16 +1060,22 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E14" s="3">
-        <v>100</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1050,61 +1089,67 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>5700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>5700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-4400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>9100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>9100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1133,8 +1178,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1151,114 +1202,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>42900</v>
+        <v>37800</v>
       </c>
       <c r="E17" s="3">
-        <v>54300</v>
+        <v>37800</v>
       </c>
       <c r="F17" s="3">
-        <v>326600</v>
+        <v>21500</v>
       </c>
       <c r="G17" s="3">
-        <v>106400</v>
+        <v>21500</v>
       </c>
       <c r="H17" s="3">
-        <v>129200</v>
+        <v>27100</v>
       </c>
       <c r="I17" s="3">
+        <v>27100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>184100</v>
+      </c>
+      <c r="K17" s="3">
         <v>204600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>18200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>18900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>41200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>32200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>29400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>80500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>46800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7700</v>
+        <v>-7500</v>
       </c>
       <c r="E18" s="3">
-        <v>-12500</v>
+        <v>-7500</v>
       </c>
       <c r="F18" s="3">
-        <v>-199200</v>
+        <v>3800</v>
       </c>
       <c r="G18" s="3">
-        <v>-21600</v>
+        <v>3800</v>
       </c>
       <c r="H18" s="3">
-        <v>-22900</v>
+        <v>-6200</v>
       </c>
       <c r="I18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-96400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-20100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-20400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-14100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-40700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-30100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,94 +1343,102 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2000</v>
+        <v>-1200</v>
       </c>
       <c r="E20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
-        <v>-18300</v>
-      </c>
       <c r="G20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>21100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>900</v>
+      </c>
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>21100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>10600</v>
+        <v>-2000</v>
       </c>
       <c r="E21" s="3">
-        <v>-11400</v>
+        <v>-2000</v>
       </c>
       <c r="F21" s="3">
-        <v>-212300</v>
+        <v>5300</v>
       </c>
       <c r="G21" s="3">
-        <v>-18600</v>
+        <v>5300</v>
       </c>
       <c r="H21" s="3">
-        <v>-32900</v>
+        <v>-5700</v>
       </c>
       <c r="I21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-101600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-14300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-8200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1384,31 +1457,37 @@
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1437,61 +1516,73 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>5800</v>
+        <v>-6400</v>
       </c>
       <c r="E23" s="3">
-        <v>-11600</v>
+        <v>-6400</v>
       </c>
       <c r="F23" s="3">
-        <v>-217500</v>
+        <v>2900</v>
       </c>
       <c r="G23" s="3">
-        <v>-21300</v>
+        <v>2900</v>
       </c>
       <c r="H23" s="3">
-        <v>-32600</v>
+        <v>-5800</v>
       </c>
       <c r="I23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-104200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-19800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>16400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-20500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-14100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-40400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-29800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,52 +1590,58 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>600</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>3400</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1596,114 +1693,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>5800</v>
+        <v>-6400</v>
       </c>
       <c r="E26" s="3">
-        <v>-12200</v>
+        <v>-6400</v>
       </c>
       <c r="F26" s="3">
-        <v>-215300</v>
+        <v>2900</v>
       </c>
       <c r="G26" s="3">
-        <v>-21800</v>
+        <v>2900</v>
       </c>
       <c r="H26" s="3">
-        <v>-32000</v>
+        <v>-6100</v>
       </c>
       <c r="I26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-104200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-20400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>12900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-20600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-14800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-40700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-30200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7000</v>
+        <v>-5500</v>
       </c>
       <c r="E27" s="3">
-        <v>-10700</v>
+        <v>-5500</v>
       </c>
       <c r="F27" s="3">
-        <v>-214900</v>
+        <v>3500</v>
       </c>
       <c r="G27" s="3">
-        <v>-21300</v>
+        <v>3500</v>
       </c>
       <c r="H27" s="3">
-        <v>-32200</v>
+        <v>-5300</v>
       </c>
       <c r="I27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="K27" s="3">
         <v>-20400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-7500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>12900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-20600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-14800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-40700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-30200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1755,8 +1870,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1767,29 +1888,29 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3">
         <v>12000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-500</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1802,14 +1923,20 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1861,8 +1988,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1914,114 +2047,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="E32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
-        <v>18300</v>
-      </c>
       <c r="G32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
-        <v>9700</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7000</v>
+        <v>-5500</v>
       </c>
       <c r="E33" s="3">
-        <v>-10700</v>
+        <v>-5500</v>
       </c>
       <c r="F33" s="3">
-        <v>-215100</v>
+        <v>3500</v>
       </c>
       <c r="G33" s="3">
-        <v>-14300</v>
+        <v>3500</v>
       </c>
       <c r="H33" s="3">
-        <v>-28800</v>
+        <v>-5300</v>
       </c>
       <c r="I33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="K33" s="3">
         <v>-20400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-8800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>12900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-20600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-14800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-40700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-30200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2073,119 +2224,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7000</v>
+        <v>-5500</v>
       </c>
       <c r="E35" s="3">
-        <v>-10700</v>
+        <v>-5500</v>
       </c>
       <c r="F35" s="3">
-        <v>-215100</v>
+        <v>3500</v>
       </c>
       <c r="G35" s="3">
-        <v>-14300</v>
+        <v>3500</v>
       </c>
       <c r="H35" s="3">
-        <v>-28800</v>
+        <v>-5300</v>
       </c>
       <c r="I35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="K35" s="3">
         <v>-20400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-8800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>12900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-20600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-14800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-40700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-30200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43373</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2205,8 +2374,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2226,75 +2397,83 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>246700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>246700</v>
+      </c>
+      <c r="F41" s="3">
         <v>279200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>279200</v>
+      </c>
+      <c r="H41" s="3">
         <v>249900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>249900</v>
+      </c>
+      <c r="J41" s="3">
         <v>259500</v>
       </c>
-      <c r="G41" s="3">
-        <v>247300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>338000</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>185500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>15400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>33000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>39200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>58800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>71700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>94900</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -2332,88 +2511,100 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>121600</v>
+        <v>11200</v>
       </c>
       <c r="E43" s="3">
-        <v>117100</v>
+        <v>11200</v>
       </c>
       <c r="F43" s="3">
-        <v>129000</v>
+        <v>60200</v>
       </c>
       <c r="G43" s="3">
-        <v>335300</v>
+        <v>60200</v>
       </c>
       <c r="H43" s="3">
-        <v>214900</v>
+        <v>49800</v>
       </c>
       <c r="I43" s="3">
+        <v>49800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>88000</v>
+      </c>
+      <c r="K43" s="3">
         <v>60600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>61300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>12700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>23600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>28300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>11900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>32700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>34800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>33800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>30400</v>
+      </c>
+      <c r="F44" s="3">
         <v>32900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
+        <v>32900</v>
+      </c>
+      <c r="H44" s="3">
         <v>42500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
+        <v>42500</v>
+      </c>
+      <c r="J44" s="3">
         <v>46300</v>
       </c>
-      <c r="G44" s="3">
-        <v>84900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>96100</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>102600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2426,11 +2617,11 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2438,41 +2629,47 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>216900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>216900</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
+        <v>82800</v>
+      </c>
+      <c r="G45" s="3">
+        <v>82800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>74000</v>
       </c>
       <c r="I45" s="3">
+        <v>74000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>47500</v>
+      </c>
+      <c r="K45" s="3">
         <v>164300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>16800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2485,37 +2682,43 @@
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>505500</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>505500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>455400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>455400</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>416200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>416200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>441200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2544,13 +2747,19 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>300</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
@@ -2573,85 +2782,97 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>9000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>9800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>11600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F48" s="3">
         <v>28400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
+        <v>28400</v>
+      </c>
+      <c r="H48" s="3">
         <v>13100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
+        <v>13100</v>
+      </c>
+      <c r="J48" s="3">
         <v>13500</v>
       </c>
-      <c r="G48" s="3">
-        <v>30100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>31700</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>34500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4200</v>
-      </c>
-      <c r="O48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>5100</v>
       </c>
       <c r="Q48" s="3">
         <v>5600</v>
       </c>
       <c r="R48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="S48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T48" s="3">
         <v>6000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2676,11 +2897,11 @@
       <c r="J49" s="3">
         <v>100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
+      <c r="K49" s="3">
+        <v>100</v>
+      </c>
+      <c r="L49" s="3">
+        <v>100</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
@@ -2694,17 +2915,23 @@
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2756,8 +2983,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2809,8 +3042,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2820,8 +3059,8 @@
       <c r="E52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
@@ -2829,41 +3068,47 @@
       <c r="H52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>53700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>37100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>28500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>57600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>35800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2915,61 +3160,73 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>525000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>525000</v>
+      </c>
+      <c r="F54" s="3">
         <v>483900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>483900</v>
+      </c>
+      <c r="H54" s="3">
         <v>429300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>429300</v>
+      </c>
+      <c r="J54" s="3">
         <v>454700</v>
       </c>
-      <c r="G54" s="3">
-        <v>713000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>695300</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>559700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>69800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>72700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>69200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>71900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>111500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>96100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>91100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>103800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>115000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2989,8 +3246,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3010,84 +3269,92 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>36700</v>
+        <v>12700</v>
       </c>
       <c r="E57" s="3">
-        <v>13900</v>
+        <v>12700</v>
       </c>
       <c r="F57" s="3">
-        <v>12800</v>
+        <v>36800</v>
       </c>
       <c r="G57" s="3">
-        <v>34900</v>
+        <v>36800</v>
       </c>
       <c r="H57" s="3">
-        <v>29500</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+        <v>14000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>14000</v>
       </c>
       <c r="J57" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>11100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>14100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>17300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3116,84 +3383,96 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>24800</v>
+        <v>40800</v>
       </c>
       <c r="E59" s="3">
-        <v>25500</v>
+        <v>40800</v>
       </c>
       <c r="F59" s="3">
-        <v>33100</v>
+        <v>9200</v>
       </c>
       <c r="G59" s="3">
-        <v>41600</v>
+        <v>9200</v>
       </c>
       <c r="H59" s="3">
-        <v>32200</v>
+        <v>7900</v>
       </c>
       <c r="I59" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="K59" s="3">
         <v>7600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>8400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>20600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>64100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>91200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>131200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>93500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>60700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>56400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>51500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>94500</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>94500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>61500</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>39300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>39300</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>45600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3222,8 +3501,14 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3240,13 +3525,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3275,8 +3560,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3295,21 +3586,21 @@
       <c r="H62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>50200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3322,14 +3613,20 @@
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3381,8 +3678,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3434,8 +3737,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3487,61 +3796,73 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>57900</v>
+        <v>94500</v>
       </c>
       <c r="E66" s="3">
-        <v>37100</v>
+        <v>94500</v>
       </c>
       <c r="F66" s="3">
-        <v>45100</v>
+        <v>61500</v>
       </c>
       <c r="G66" s="3">
-        <v>75900</v>
+        <v>61500</v>
       </c>
       <c r="H66" s="3">
-        <v>61900</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
+        <v>39400</v>
+      </c>
+      <c r="I66" s="3">
+        <v>39400</v>
       </c>
       <c r="J66" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
         <v>9500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>70800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>64100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>92200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>132200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>95200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>76400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>78700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>79700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3561,8 +3882,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3614,8 +3937,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3667,8 +3996,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3720,8 +4055,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3773,61 +4114,73 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-276500</v>
+        <v>-287600</v>
       </c>
       <c r="E72" s="3">
-        <v>-283600</v>
+        <v>-287600</v>
       </c>
       <c r="F72" s="3">
+        <v>-276700</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-276700</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-283700</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-283700</v>
+      </c>
+      <c r="J72" s="3">
         <v>-272900</v>
       </c>
-      <c r="G72" s="3">
-        <v>-43400</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-43400</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-14600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-8700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-293100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-306000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-303800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-283200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-268300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-257300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-246700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-221700</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3879,8 +4232,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3932,8 +4291,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3985,61 +4350,73 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>436000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>436000</v>
+      </c>
+      <c r="F76" s="3">
         <v>426000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>426000</v>
+      </c>
+      <c r="H76" s="3">
         <v>392300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>392300</v>
+      </c>
+      <c r="J76" s="3">
         <v>409600</v>
       </c>
-      <c r="G76" s="3">
-        <v>637100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>633400</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>559800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>60200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-20300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-20700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>25100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>35300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4091,119 +4468,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43373</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7000</v>
+        <v>-5500</v>
       </c>
       <c r="E81" s="3">
-        <v>-10700</v>
+        <v>-5500</v>
       </c>
       <c r="F81" s="3">
-        <v>-215100</v>
+        <v>3500</v>
       </c>
       <c r="G81" s="3">
-        <v>-14300</v>
+        <v>3500</v>
       </c>
       <c r="H81" s="3">
-        <v>-28800</v>
+        <v>-5300</v>
       </c>
       <c r="I81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="K81" s="3">
         <v>-20400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-8800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>12900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-20600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-14800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-40700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-30200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4223,40 +4618,42 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4900</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>5300</v>
+        <v>3000</v>
       </c>
       <c r="G83" s="3">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="H83" s="3">
-        <v>-300</v>
+        <v>1300</v>
       </c>
       <c r="I83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>5500</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
@@ -4270,14 +4667,20 @@
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4329,8 +4732,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4382,8 +4791,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4435,8 +4850,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4488,8 +4909,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4541,61 +4968,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>11700</v>
+        <v>-26700</v>
       </c>
       <c r="E89" s="3">
-        <v>-2000</v>
+        <v>-26700</v>
       </c>
       <c r="F89" s="3">
-        <v>31400</v>
+        <v>5800</v>
       </c>
       <c r="G89" s="3">
-        <v>-104300</v>
+        <v>5800</v>
       </c>
       <c r="H89" s="3">
-        <v>120600</v>
+        <v>-1000</v>
       </c>
       <c r="I89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-339200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-43600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-36600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-35300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-22900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4615,61 +5054,69 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-34200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-10700</v>
       </c>
       <c r="L91" s="3">
         <v>-10700</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="M91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4721,8 +5168,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4774,61 +5227,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-17600</v>
-      </c>
-      <c r="G94" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-30700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>3000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4848,31 +5313,33 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4901,8 +5368,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4954,8 +5427,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5007,8 +5486,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5060,163 +5545,187 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>17900</v>
+        <v>12300</v>
       </c>
       <c r="E100" s="3">
-        <v>-300</v>
+        <v>12300</v>
       </c>
       <c r="F100" s="3">
-        <v>16200</v>
+        <v>8900</v>
       </c>
       <c r="G100" s="3">
-        <v>18500</v>
+        <v>8900</v>
       </c>
       <c r="H100" s="3">
-        <v>32300</v>
+        <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K100" s="3">
         <v>551800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>43600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>7700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-300</v>
+        <v>-3700</v>
       </c>
       <c r="E101" s="3">
-        <v>-7300</v>
+        <v>-3700</v>
       </c>
       <c r="F101" s="3">
-        <v>-17800</v>
+        <v>-8900</v>
       </c>
       <c r="G101" s="3">
-        <v>-6400</v>
+        <v>-8900</v>
       </c>
       <c r="H101" s="3">
-        <v>-1100</v>
+        <v>-3200</v>
       </c>
       <c r="I101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
         <v>2900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>29300</v>
+        <v>-16200</v>
       </c>
       <c r="E102" s="3">
-        <v>-9600</v>
+        <v>-16200</v>
       </c>
       <c r="F102" s="3">
-        <v>12100</v>
+        <v>14600</v>
       </c>
       <c r="G102" s="3">
-        <v>-90700</v>
+        <v>14600</v>
       </c>
       <c r="H102" s="3">
-        <v>149500</v>
+        <v>-4800</v>
       </c>
       <c r="I102" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K102" s="3">
         <v>184800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>3700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-40700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-36100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-23200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>15400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>SOS</t>
   </si>
@@ -656,198 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43373</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43190</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>85500</v>
+      </c>
+      <c r="F8" s="3">
         <v>30300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>30300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>25300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>25300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>20900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>20900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>87600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>184500</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>9900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>14200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>5100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>20800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>18100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>17600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>39800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>16700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>83200</v>
+      </c>
+      <c r="F9" s="3">
         <v>29000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>29000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>18300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>18300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>20900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>20900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>94200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>167200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>9800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -866,47 +879,53 @@
       <c r="U9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>7000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>7000</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>-6600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>17300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -925,8 +944,14 @@
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -948,8 +973,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -983,32 +1010,38 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>4600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>8400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>4200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1066,8 +1099,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1077,11 +1116,11 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1089,74 +1128,80 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>5700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>5700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>-4400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>9100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>9100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F15" s="3">
         <v>4400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>4400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>2400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1184,8 +1229,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1204,126 +1255,140 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>88700</v>
+      </c>
+      <c r="F17" s="3">
         <v>37800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>37800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>21500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>21500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>27100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>27100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>184100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>204600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>18200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>18900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>41200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>32200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>29400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>80500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>46800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-96400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-20100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-7600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-8300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-14100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-11800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-40700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-30100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1345,106 +1410,114 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>21100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>5300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-5700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-101600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-14300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-7500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-8200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1463,8 +1536,14 @@
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1489,11 +1568,11 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1522,75 +1601,87 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-104200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-19800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-8200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>16400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-14100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-11000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-40400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-29800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1599,49 +1690,55 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>3400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1699,126 +1796,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-6400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-6100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-104200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-20400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>12900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-14800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-11000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-40700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-30200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-5300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-107600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-20400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>12900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-14800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-11000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-40700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-30200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1876,8 +1991,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1900,23 +2021,23 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-3600</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3">
         <v>12000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-500</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1929,14 +2050,20 @@
       <c r="S29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1994,8 +2121,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2053,126 +2186,144 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-21100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-107600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-20400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-8800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>12900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-14800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-11000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-40700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-30200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2230,131 +2381,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-107600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-20400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-8800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>12900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-14800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-11000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-40700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-30200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43373</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43190</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2376,8 +2545,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,67 +2570,75 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>237500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>237500</v>
+      </c>
+      <c r="F41" s="3">
         <v>246700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>246700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>279200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>279200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>249900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>249900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>259500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>185500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>15500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>33000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>39200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>58800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>71700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>94900</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2470,17 +2649,17 @@
         <v>200</v>
       </c>
       <c r="F42" s="3">
+        <v>200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>200</v>
+      </c>
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2517,100 +2696,112 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>164600</v>
+      </c>
+      <c r="F43" s="3">
         <v>11200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>11200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>60200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>60200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>49800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>49800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>88000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>60600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>61300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>12700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>23600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>28300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>11900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>32700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>34800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>33800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F44" s="3">
         <v>30400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>30400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>32900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>32900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>42500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>42500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>46300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>102600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2623,11 +2814,11 @@
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -2635,47 +2826,53 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>29900</v>
+      </c>
+      <c r="F45" s="3">
         <v>216900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>216900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>82800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>82800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>74000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>74000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>47500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>164300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3">
         <v>16800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2688,44 +2885,50 @@
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>465100</v>
+      </c>
+      <c r="F46" s="3">
         <v>505500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>505500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>455400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>455400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>416200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>416200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>441200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2753,8 +2956,14 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2788,91 +2997,103 @@
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>9000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>9800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>11600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F48" s="3">
         <v>19400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>19400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>28400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>28400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>13100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>13100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>13500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>34500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>5100</v>
       </c>
       <c r="S48" s="3">
         <v>5600</v>
       </c>
       <c r="T48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="U48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="V48" s="3">
         <v>6000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2903,11 +3124,11 @@
       <c r="L49" s="3">
         <v>100</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
+      <c r="M49" s="3">
+        <v>100</v>
+      </c>
+      <c r="N49" s="3">
+        <v>100</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
@@ -2921,17 +3142,23 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2989,8 +3216,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3048,8 +3281,14 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3074,41 +3313,47 @@
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>53700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>37100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>28500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>57600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>35800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3166,67 +3411,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>482400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>482400</v>
+      </c>
+      <c r="F54" s="3">
         <v>525000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>525000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>483900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>483900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>429300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>429300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>454700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>559700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>69800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>72700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>69200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>71900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>111500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>96100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>91100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>103800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>115000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3248,8 +3505,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3271,97 +3530,105 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F57" s="3">
         <v>12700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>12700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>36800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>36800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>14000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>12900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>11100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>14100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>17300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3389,97 +3656,109 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F59" s="3">
         <v>40800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>40800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>9200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>9200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>7900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>7900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>11800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>7600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>8400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>20600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>64100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>91200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>131200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>93500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>60700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>56400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>51500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F60" s="3">
         <v>94500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>94500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>61500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>61500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>39300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>39300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>45600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3507,8 +3786,14 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3525,20 +3810,20 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3566,8 +3851,14 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3592,21 +3883,21 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3">
         <v>50200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3619,14 +3910,20 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3684,8 +3981,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3743,8 +4046,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3802,67 +4111,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F66" s="3">
         <v>94500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>94500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>61500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>61500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>39400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>39400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>46000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3">
         <v>9500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>70800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>64100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>92200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>132200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>95200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>76400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>78700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>79700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3884,8 +4205,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3943,8 +4266,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4002,8 +4331,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4061,8 +4396,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4120,67 +4461,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-290300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-290300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-287600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-287600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-276700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-276700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-283700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-283700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-272900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-14600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-8700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-293100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-306000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-303800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-283200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-268300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-257300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-246700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-221700</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4238,8 +4591,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4297,8 +4656,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4356,67 +4721,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>441900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>441900</v>
+      </c>
+      <c r="F76" s="3">
         <v>436000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>436000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>426000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>426000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>392300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>392300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>409600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>559800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>60200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-20300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>14700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>25100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>35300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4474,131 +4851,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43373</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43190</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-107600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-20400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-8800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>12900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-14800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-11000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-40700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-30200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4620,46 +5015,48 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>5500</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
@@ -4673,14 +5070,20 @@
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4738,8 +5141,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4797,8 +5206,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4856,8 +5271,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4915,8 +5336,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4974,67 +5401,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-26700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-26700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>15700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-339200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-43600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>500</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
         <v>-36600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-26900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-35300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-22900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5056,8 +5495,10 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5079,44 +5520,50 @@
       <c r="I91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-10700</v>
       </c>
       <c r="N91" s="3">
         <v>-10700</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="O91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-12100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5174,8 +5621,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5233,8 +5686,14 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5256,44 +5715,50 @@
       <c r="I94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-30700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>3000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
         <v>-2800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-12100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5315,8 +5780,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5341,11 +5808,11 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5374,8 +5841,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5433,8 +5906,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5492,8 +5971,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5551,181 +6036,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>12300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>12300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>8900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>8900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>8100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>551800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>43600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>7700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-8900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-8900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-3200</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
         <v>2900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
         <v>-1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-16200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-16200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>14600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>14600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>184800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
         <v>-40700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-31800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-36100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-23200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>15400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>SOS</t>
   </si>
@@ -766,11 +766,11 @@
       <c r="E8" s="3">
         <v>85500</v>
       </c>
-      <c r="F8" s="3">
-        <v>30300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>30300</v>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H8" s="3">
         <v>25300</v>
@@ -831,11 +831,11 @@
       <c r="E9" s="3">
         <v>83200</v>
       </c>
-      <c r="F9" s="3">
-        <v>29000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>29000</v>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H9" s="3">
         <v>18300</v>
@@ -896,11 +896,11 @@
       <c r="E10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1200</v>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H10" s="3">
         <v>7000</v>
@@ -1182,10 +1182,10 @@
         <v>1100</v>
       </c>
       <c r="F15" s="3">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>2400</v>
@@ -1268,11 +1268,11 @@
       <c r="E17" s="3">
         <v>88700</v>
       </c>
-      <c r="F17" s="3">
-        <v>37800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>37800</v>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H17" s="3">
         <v>21500</v>
@@ -1333,11 +1333,11 @@
       <c r="E18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-7500</v>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H18" s="3">
         <v>3800</v>
@@ -1423,11 +1423,11 @@
       <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1200</v>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="3">
         <v>1000</v>
@@ -1489,10 +1489,10 @@
         <v>-500</v>
       </c>
       <c r="F21" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>5300</v>
@@ -1618,11 +1618,11 @@
       <c r="E23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-6400</v>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="3">
         <v>2900</v>
@@ -1683,11 +1683,11 @@
       <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1813,11 +1813,11 @@
       <c r="E26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-6400</v>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H26" s="3">
         <v>2900</v>
@@ -1878,11 +1878,11 @@
       <c r="E27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-5500</v>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H27" s="3">
         <v>3500</v>
@@ -2203,11 +2203,11 @@
       <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1200</v>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H32" s="3">
         <v>-1000</v>
@@ -2268,11 +2268,11 @@
       <c r="E33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-5500</v>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H33" s="3">
         <v>3500</v>
@@ -2398,11 +2398,11 @@
       <c r="E35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-5500</v>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H35" s="3">
         <v>3500</v>
@@ -2583,11 +2583,11 @@
       <c r="E41" s="3">
         <v>237500</v>
       </c>
-      <c r="F41" s="3">
-        <v>246700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>246700</v>
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H41" s="3">
         <v>279200</v>
@@ -2649,10 +2649,10 @@
         <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>300</v>
@@ -2708,16 +2708,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>164600</v>
+        <v>32800</v>
       </c>
       <c r="E43" s="3">
-        <v>164600</v>
-      </c>
-      <c r="F43" s="3">
-        <v>11200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>11200</v>
+        <v>32800</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H43" s="3">
         <v>60200</v>
@@ -2778,11 +2778,11 @@
       <c r="E44" s="3">
         <v>33000</v>
       </c>
-      <c r="F44" s="3">
-        <v>30400</v>
-      </c>
-      <c r="G44" s="3">
-        <v>30400</v>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H44" s="3">
         <v>32900</v>
@@ -2838,16 +2838,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>29900</v>
+        <v>161600</v>
       </c>
       <c r="E45" s="3">
-        <v>29900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>216900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>216900</v>
+        <v>161600</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3">
         <v>82800</v>
@@ -2908,11 +2908,11 @@
       <c r="E46" s="3">
         <v>465100</v>
       </c>
-      <c r="F46" s="3">
-        <v>505500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>505500</v>
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H46" s="3">
         <v>455400</v>
@@ -3038,11 +3038,11 @@
       <c r="E48" s="3">
         <v>17100</v>
       </c>
-      <c r="F48" s="3">
-        <v>19400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>19400</v>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H48" s="3">
         <v>28400</v>
@@ -3103,11 +3103,11 @@
       <c r="E49" s="3">
         <v>100</v>
       </c>
-      <c r="F49" s="3">
-        <v>100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>100</v>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H49" s="3">
         <v>100</v>
@@ -3428,11 +3428,11 @@
       <c r="E54" s="3">
         <v>482400</v>
       </c>
-      <c r="F54" s="3">
-        <v>525000</v>
-      </c>
-      <c r="G54" s="3">
-        <v>525000</v>
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H54" s="3">
         <v>483900</v>
@@ -3543,11 +3543,11 @@
       <c r="E57" s="3">
         <v>12500</v>
       </c>
-      <c r="F57" s="3">
-        <v>12700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>12700</v>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H57" s="3">
         <v>36800</v>
@@ -3608,11 +3608,11 @@
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3">
-        <v>100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>100</v>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
@@ -3668,16 +3668,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12700</v>
+        <v>12600</v>
       </c>
       <c r="E59" s="3">
-        <v>12700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>40800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>40800</v>
+        <v>12600</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H59" s="3">
         <v>9200</v>
@@ -3738,11 +3738,11 @@
       <c r="E60" s="3">
         <v>46700</v>
       </c>
-      <c r="F60" s="3">
-        <v>94500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>94500</v>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H60" s="3">
         <v>61500</v>
@@ -4128,11 +4128,11 @@
       <c r="E66" s="3">
         <v>46700</v>
       </c>
-      <c r="F66" s="3">
-        <v>94500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>94500</v>
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H66" s="3">
         <v>61500</v>
@@ -4473,25 +4473,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-290300</v>
+        <v>-290100</v>
       </c>
       <c r="E72" s="3">
-        <v>-290300</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-287600</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-287600</v>
+        <v>-290100</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H72" s="3">
-        <v>-276700</v>
+        <v>-276500</v>
       </c>
       <c r="I72" s="3">
-        <v>-276700</v>
+        <v>-276500</v>
       </c>
       <c r="J72" s="3">
-        <v>-283700</v>
+        <v>-283600</v>
       </c>
       <c r="K72" s="3">
         <v>-283700</v>
@@ -4738,11 +4738,11 @@
       <c r="E76" s="3">
         <v>441900</v>
       </c>
-      <c r="F76" s="3">
-        <v>436000</v>
-      </c>
-      <c r="G76" s="3">
-        <v>436000</v>
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H76" s="3">
         <v>426000</v>
@@ -4938,11 +4938,11 @@
       <c r="E81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-5500</v>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H81" s="3">
         <v>3500</v>
@@ -5418,11 +5418,11 @@
       <c r="E89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
-        <v>-26700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-26700</v>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H89" s="3">
         <v>5800</v>
@@ -6053,11 +6053,11 @@
       <c r="E100" s="3">
         <v>0</v>
       </c>
-      <c r="F100" s="3">
-        <v>12300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>12300</v>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H100" s="3">
         <v>8900</v>
@@ -6184,10 +6184,10 @@
         <v>-4600</v>
       </c>
       <c r="F102" s="3">
-        <v>-16200</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-16200</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>14600</v>

--- a/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>SOS</t>
   </si>
@@ -656,64 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44926</v>
       </c>
       <c r="K7" s="2">
         <v>45016</v>
@@ -722,63 +722,69 @@
         <v>44926</v>
       </c>
       <c r="M7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="N7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43190</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>32300</v>
+      </c>
+      <c r="F8" s="3">
         <v>85500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>85500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>25300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>25300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>20900</v>
-      </c>
-      <c r="I8" s="3">
-        <v>20900</v>
-      </c>
-      <c r="J8" s="3">
-        <v>87600</v>
       </c>
       <c r="K8" s="3">
         <v>20900</v>
@@ -787,63 +793,69 @@
         <v>87600</v>
       </c>
       <c r="M8" s="3">
+        <v>20900</v>
+      </c>
+      <c r="N8" s="3">
+        <v>87600</v>
+      </c>
+      <c r="O8" s="3">
         <v>184500</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>9900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>14200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>5100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>20800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>18100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>17600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>39800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>16700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>40000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>30600</v>
+      </c>
+      <c r="F9" s="3">
         <v>83200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>83200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>18300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>18300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>20900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>20900</v>
-      </c>
-      <c r="J9" s="3">
-        <v>94200</v>
       </c>
       <c r="K9" s="3">
         <v>20900</v>
@@ -852,20 +864,20 @@
         <v>94200</v>
       </c>
       <c r="M9" s="3">
+        <v>20900</v>
+      </c>
+      <c r="N9" s="3">
+        <v>94200</v>
+      </c>
+      <c r="O9" s="3">
         <v>167200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>9800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -884,31 +896,37 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>7000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>7000</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
-        <v>-6600</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -917,20 +935,20 @@
         <v>-6600</v>
       </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="O10" s="3">
         <v>17300</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -949,8 +967,14 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +998,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1015,32 +1041,38 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>3400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>4600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>8400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>4200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1136,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1115,11 +1153,11 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1127,8 +1165,8 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1139,61 +1177,67 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>5700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>5700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>-4400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>9100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>9100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>2400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2800</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1202,10 +1246,10 @@
         <v>2800</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1234,8 +1278,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,31 +1306,33 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>74200</v>
+      </c>
+      <c r="F17" s="3">
         <v>88700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>88700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>21500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>21500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>27100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>27100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>184100</v>
       </c>
       <c r="K17" s="3">
         <v>27100</v>
@@ -1289,63 +1341,69 @@
         <v>184100</v>
       </c>
       <c r="M17" s="3">
+        <v>27100</v>
+      </c>
+      <c r="N17" s="3">
+        <v>184100</v>
+      </c>
+      <c r="O17" s="3">
         <v>204600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>18200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>18900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>41200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>32200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>29400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>80500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>46800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-96400</v>
       </c>
       <c r="K18" s="3">
         <v>-6200</v>
@@ -1354,40 +1412,46 @@
         <v>-96400</v>
       </c>
       <c r="M18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-96400</v>
+      </c>
+      <c r="O18" s="3">
         <v>-20100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-7600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-8300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-20400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-14100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-11800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-40700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-30100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,31 +1475,33 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>8000</v>
       </c>
       <c r="K20" s="3">
         <v>-500</v>
@@ -1444,63 +1510,69 @@
         <v>8000</v>
       </c>
       <c r="M20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>21100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>5300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-5700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-101600</v>
       </c>
       <c r="K21" s="3">
         <v>-5700</v>
@@ -1509,20 +1581,20 @@
         <v>-101600</v>
       </c>
       <c r="M21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-101600</v>
+      </c>
+      <c r="O21" s="3">
         <v>-14300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-7500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-8200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1541,8 +1613,14 @@
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1573,11 +1651,11 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1606,31 +1684,37 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-104200</v>
       </c>
       <c r="K23" s="3">
         <v>-5800</v>
@@ -1639,63 +1723,69 @@
         <v>-104200</v>
       </c>
       <c r="M23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-104200</v>
+      </c>
+      <c r="O23" s="3">
         <v>-19800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-8200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>16400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-20500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-14100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-11000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-40400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-29800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
@@ -1704,40 +1794,46 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,31 +1897,37 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-6100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-104200</v>
       </c>
       <c r="K26" s="3">
         <v>-6100</v>
@@ -1834,63 +1936,69 @@
         <v>-104200</v>
       </c>
       <c r="M26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-104200</v>
+      </c>
+      <c r="O26" s="3">
         <v>-20400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-8200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>12900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-20600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-14800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-11000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-40700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-30200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-5300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-107600</v>
       </c>
       <c r="K27" s="3">
         <v>-5300</v>
@@ -1899,40 +2007,46 @@
         <v>-107600</v>
       </c>
       <c r="M27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="O27" s="3">
         <v>-20400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-8200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>12900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-20600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-14800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-11000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-40700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-30200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2110,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2020,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-3600</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2028,21 +2148,21 @@
       <c r="L29" s="3">
         <v>-3600</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3">
         <v>12000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-500</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2055,14 +2175,20 @@
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2252,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,31 +2323,37 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>300</v>
+      </c>
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-8000</v>
       </c>
       <c r="K32" s="3">
         <v>500</v>
@@ -2224,63 +2362,69 @@
         <v>-8000</v>
       </c>
       <c r="M32" s="3">
+        <v>500</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-5300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-107600</v>
       </c>
       <c r="K33" s="3">
         <v>-5300</v>
@@ -2289,40 +2433,46 @@
         <v>-107600</v>
       </c>
       <c r="M33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="O33" s="3">
         <v>-20400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-8800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>12900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-20600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-14800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-11000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-40700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-30200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,31 +2536,37 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-5300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-107600</v>
       </c>
       <c r="K35" s="3">
         <v>-5300</v>
@@ -2419,68 +2575,74 @@
         <v>-107600</v>
       </c>
       <c r="M35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="O35" s="3">
         <v>-20400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-8800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>12900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-20600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-14800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-11000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-40700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-30200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44926</v>
       </c>
       <c r="K38" s="2">
         <v>45016</v>
@@ -2489,40 +2651,46 @@
         <v>44926</v>
       </c>
       <c r="M38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="N38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43190</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2714,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,31 +2741,33 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F41" s="3">
         <v>237500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>237500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>279200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>279200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>249900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>249900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>259500</v>
       </c>
       <c r="K41" s="3">
         <v>249900</v>
@@ -2604,61 +2776,67 @@
         <v>259500</v>
       </c>
       <c r="M41" s="3">
+        <v>249900</v>
+      </c>
+      <c r="N41" s="3">
+        <v>259500</v>
+      </c>
+      <c r="O41" s="3">
         <v>185500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>12500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>33000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>39200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>58800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>71700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>94900</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2701,31 +2879,37 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>354900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>354900</v>
+      </c>
+      <c r="F43" s="3">
         <v>32800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>32800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>60200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>60200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>49800</v>
-      </c>
-      <c r="I43" s="3">
-        <v>49800</v>
-      </c>
-      <c r="J43" s="3">
-        <v>88000</v>
       </c>
       <c r="K43" s="3">
         <v>49800</v>
@@ -2734,63 +2918,69 @@
         <v>88000</v>
       </c>
       <c r="M43" s="3">
+        <v>49800</v>
+      </c>
+      <c r="N43" s="3">
+        <v>88000</v>
+      </c>
+      <c r="O43" s="3">
         <v>60600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>61300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>12700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>23600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>28300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>11900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>32700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>34800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>33800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F44" s="3">
         <v>33000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>33000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>32900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>32900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>42500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>42500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>46300</v>
       </c>
       <c r="K44" s="3">
         <v>42500</v>
@@ -2799,14 +2989,14 @@
         <v>46300</v>
       </c>
       <c r="M44" s="3">
+        <v>42500</v>
+      </c>
+      <c r="N44" s="3">
+        <v>46300</v>
+      </c>
+      <c r="O44" s="3">
         <v>102600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2819,11 +3009,11 @@
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -2831,31 +3021,37 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>79100</v>
+      </c>
+      <c r="F45" s="3">
         <v>161600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>161600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>82800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>82800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>74000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>74000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>47500</v>
       </c>
       <c r="K45" s="3">
         <v>74000</v>
@@ -2864,20 +3060,20 @@
         <v>47500</v>
       </c>
       <c r="M45" s="3">
+        <v>74000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>47500</v>
+      </c>
+      <c r="O45" s="3">
         <v>164300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3">
         <v>16800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,37 +3086,43 @@
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>463400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>463400</v>
+      </c>
+      <c r="F46" s="3">
         <v>465100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>465100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>455400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>455400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>416200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>416200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>441200</v>
       </c>
       <c r="K46" s="3">
         <v>416200</v>
@@ -2929,10 +3131,10 @@
         <v>441200</v>
       </c>
       <c r="M46" s="3">
-        <v>0</v>
+        <v>416200</v>
       </c>
       <c r="N46" s="3">
-        <v>0</v>
+        <v>441200</v>
       </c>
       <c r="O46" s="3">
         <v>0</v>
@@ -2961,8 +3163,14 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3002,55 +3210,61 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>9000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>9800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>11600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F48" s="3">
         <v>17100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>17100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>28400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>28400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>13100</v>
-      </c>
-      <c r="I48" s="3">
-        <v>13100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>13500</v>
       </c>
       <c r="K48" s="3">
         <v>13100</v>
@@ -3059,40 +3273,46 @@
         <v>13500</v>
       </c>
       <c r="M48" s="3">
+        <v>13100</v>
+      </c>
+      <c r="N48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="O48" s="3">
         <v>34500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4200</v>
-      </c>
-      <c r="S48" s="3">
-        <v>5600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>5100</v>
       </c>
       <c r="U48" s="3">
         <v>5600</v>
       </c>
       <c r="V48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="W48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="X48" s="3">
         <v>6000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3129,11 +3349,11 @@
       <c r="N49" s="3">
         <v>100</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
+      <c r="O49" s="3">
+        <v>100</v>
+      </c>
+      <c r="P49" s="3">
+        <v>100</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
@@ -3147,17 +3367,23 @@
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3447,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3518,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3318,41 +3556,47 @@
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
         <v>53700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>37100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>28500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>57600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>35800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>14700</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,31 +3660,37 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>465100</v>
+      </c>
+      <c r="F54" s="3">
         <v>482400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>482400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>483900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>483900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>429300</v>
-      </c>
-      <c r="I54" s="3">
-        <v>429300</v>
-      </c>
-      <c r="J54" s="3">
-        <v>454700</v>
       </c>
       <c r="K54" s="3">
         <v>429300</v>
@@ -3449,40 +3699,46 @@
         <v>454700</v>
       </c>
       <c r="M54" s="3">
+        <v>429300</v>
+      </c>
+      <c r="N54" s="3">
+        <v>454700</v>
+      </c>
+      <c r="O54" s="3">
         <v>559700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>69800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>72700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>69200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>71900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>111500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>96100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>91100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>103800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>115000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3762,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,31 +3789,33 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>19300</v>
+      </c>
+      <c r="F57" s="3">
         <v>12500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>12500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>36800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>36800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>14000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>14000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>12900</v>
       </c>
       <c r="K57" s="3">
         <v>14000</v>
@@ -3563,41 +3823,47 @@
       <c r="L57" s="3">
         <v>12900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
+      <c r="M57" s="3">
+        <v>14000</v>
       </c>
       <c r="N57" s="3">
+        <v>12900</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>11100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>14100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>17300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3608,19 +3874,19 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>600</v>
@@ -3629,10 +3895,10 @@
         <v>500</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3661,31 +3927,37 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F59" s="3">
         <v>12600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>12600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>9200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>9200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>7900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>7900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>11800</v>
       </c>
       <c r="K59" s="3">
         <v>7900</v>
@@ -3694,63 +3966,69 @@
         <v>11800</v>
       </c>
       <c r="M59" s="3">
+        <v>7900</v>
+      </c>
+      <c r="N59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="O59" s="3">
         <v>7600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>8400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>20600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>64100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>91200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>131200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>93500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>60700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>56400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>51500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>41900</v>
+      </c>
+      <c r="F60" s="3">
         <v>46700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>46700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>61500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>61500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>39300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>39300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>45600</v>
       </c>
       <c r="K60" s="3">
         <v>39300</v>
@@ -3759,10 +4037,10 @@
         <v>45600</v>
       </c>
       <c r="M60" s="3">
-        <v>0</v>
+        <v>39300</v>
       </c>
       <c r="N60" s="3">
-        <v>0</v>
+        <v>45600</v>
       </c>
       <c r="O60" s="3">
         <v>0</v>
@@ -3791,8 +4069,14 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3809,13 +4093,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>100</v>
-      </c>
-      <c r="J61" s="3">
-        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>100</v>
@@ -3824,10 +4108,10 @@
         <v>400</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3856,8 +4140,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3888,21 +4178,21 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
         <v>50200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3915,14 +4205,20 @@
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4282,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4353,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,31 +4424,37 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>41900</v>
+      </c>
+      <c r="F66" s="3">
         <v>46700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>46700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>61500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>61500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>39400</v>
-      </c>
-      <c r="I66" s="3">
-        <v>39400</v>
-      </c>
-      <c r="J66" s="3">
-        <v>46000</v>
       </c>
       <c r="K66" s="3">
         <v>39400</v>
@@ -4148,41 +4462,47 @@
       <c r="L66" s="3">
         <v>46000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
+      <c r="M66" s="3">
+        <v>39400</v>
       </c>
       <c r="N66" s="3">
+        <v>46000</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" s="3">
         <v>9500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>70800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>64100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>92200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>132200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>95200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>76400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>78700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>79700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>78500</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4526,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4593,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4664,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4735,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4806,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-337700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-337700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-290100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-290100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-276500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-276500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-283600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-283600</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-272900</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-283700</v>
       </c>
       <c r="L72" s="3">
         <v>-272900</v>
       </c>
       <c r="M72" s="3">
+        <v>-283700</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-272900</v>
+      </c>
+      <c r="O72" s="3">
         <v>-14600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-8700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-293100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-306000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-303800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-283200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-268300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-257300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-246700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-221700</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4948,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +5019,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,31 +5090,37 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>423100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>423100</v>
+      </c>
+      <c r="F76" s="3">
         <v>441900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>441900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>426000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>426000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>392300</v>
-      </c>
-      <c r="I76" s="3">
-        <v>392300</v>
-      </c>
-      <c r="J76" s="3">
-        <v>409600</v>
       </c>
       <c r="K76" s="3">
         <v>392300</v>
@@ -4759,40 +5129,46 @@
         <v>409600</v>
       </c>
       <c r="M76" s="3">
+        <v>392300</v>
+      </c>
+      <c r="N76" s="3">
+        <v>409600</v>
+      </c>
+      <c r="O76" s="3">
         <v>559800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>60200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-20300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-20700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>14700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>25100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>35300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>59000</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,36 +5232,42 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44926</v>
       </c>
       <c r="K80" s="2">
         <v>45016</v>
@@ -4894,63 +5276,69 @@
         <v>44926</v>
       </c>
       <c r="M80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="N80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43190</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-5300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-107600</v>
       </c>
       <c r="K81" s="3">
         <v>-5300</v>
@@ -4959,40 +5347,46 @@
         <v>-107600</v>
       </c>
       <c r="M81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="O81" s="3">
         <v>-20400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-8800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>12900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-20600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-14800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-11000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-40700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-30200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,31 +5410,33 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>1300</v>
@@ -5049,19 +5445,19 @@
         <v>5</v>
       </c>
       <c r="M83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
         <v>5500</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
@@ -5075,14 +5471,20 @@
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5548,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5619,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5690,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5761,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,31 +5832,37 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>15700</v>
       </c>
       <c r="K89" s="3">
         <v>-1000</v>
@@ -5439,40 +5871,46 @@
         <v>15700</v>
       </c>
       <c r="M89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N89" s="3">
+        <v>15700</v>
+      </c>
+      <c r="O89" s="3">
         <v>-339200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-43600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>500</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>-36600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-26900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-35300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-22900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,16 +5934,18 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
@@ -5519,8 +5959,8 @@
       <c r="I91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J91" s="3">
-        <v>-8000</v>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
@@ -5528,41 +5968,47 @@
       <c r="L91" s="3">
         <v>-8000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-10700</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-10700</v>
       </c>
       <c r="P91" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="Q91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-12100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +6072,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,16 +6143,22 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>5</v>
@@ -5714,8 +6172,8 @@
       <c r="I94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J94" s="3">
-        <v>-8800</v>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -5723,41 +6181,47 @@
       <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="O94" s="3">
         <v>-30700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>3000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-12100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6245,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5813,11 +6279,11 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5846,8 +6312,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6383,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6454,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,31 +6525,37 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>8900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>8900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>8100</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
@@ -6074,63 +6564,69 @@
         <v>8100</v>
       </c>
       <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
+        <v>8100</v>
+      </c>
+      <c r="O100" s="3">
         <v>551800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>43600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>7700</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-8900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-8900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-3200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>-3200</v>
@@ -6139,63 +6635,69 @@
         <v>5</v>
       </c>
       <c r="M101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
         <v>2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>-1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>14600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>14600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4800</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="J102" s="3">
-        <v>6100</v>
       </c>
       <c r="K102" s="3">
         <v>-4800</v>
@@ -6204,36 +6706,42 @@
         <v>6100</v>
       </c>
       <c r="M102" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="N102" s="3">
+        <v>6100</v>
+      </c>
+      <c r="O102" s="3">
         <v>184800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>3700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>-40700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-31800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-36100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-23200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>15400</v>
       </c>
     </row>
